--- a/output/yearly_total_coral_cover_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_19_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.263810137435043</v>
+        <v>1.246717909904105</v>
       </c>
       <c r="C3" t="n">
-        <v>4.582893404011584</v>
+        <v>4.729684320750568</v>
       </c>
       <c r="D3" t="n">
-        <v>6.059881977044768</v>
+        <v>6.057643592279086</v>
       </c>
       <c r="E3" t="n">
-        <v>11.90658551849139</v>
+        <v>12.03404582293376</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.404776888813214</v>
+        <v>1.373790676320513</v>
       </c>
       <c r="C4" t="n">
-        <v>4.99782606335252</v>
+        <v>5.407178795771109</v>
       </c>
       <c r="D4" t="n">
-        <v>6.31745511528218</v>
+        <v>6.263858932824904</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72005806744791</v>
+        <v>13.04482840491653</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.597552195269534</v>
+        <v>1.545511253329686</v>
       </c>
       <c r="C5" t="n">
-        <v>5.539549151671696</v>
+        <v>6.334604218133103</v>
       </c>
       <c r="D5" t="n">
-        <v>6.634926557506378</v>
+        <v>6.512690500871828</v>
       </c>
       <c r="E5" t="n">
-        <v>13.77202790444761</v>
+        <v>14.39280597233462</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.81223421864948</v>
+        <v>1.738044040212375</v>
       </c>
       <c r="C6" t="n">
-        <v>6.197836447054883</v>
+        <v>7.468212795762913</v>
       </c>
       <c r="D6" t="n">
-        <v>6.988172428545449</v>
+        <v>6.729656458639666</v>
       </c>
       <c r="E6" t="n">
-        <v>14.99824309424981</v>
+        <v>15.93591329461495</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.051738055251866</v>
+        <v>1.950659489152204</v>
       </c>
       <c r="C7" t="n">
-        <v>6.96509236809795</v>
+        <v>8.746573548725184</v>
       </c>
       <c r="D7" t="n">
-        <v>7.404186245785261</v>
+        <v>7.030395265091879</v>
       </c>
       <c r="E7" t="n">
-        <v>16.42101666913508</v>
+        <v>17.72762830296926</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.257632187993152</v>
+        <v>1.181423621671696</v>
       </c>
       <c r="C8" t="n">
-        <v>4.606860391557036</v>
+        <v>6.408340523456359</v>
       </c>
       <c r="D8" t="n">
-        <v>5.619430809739538</v>
+        <v>5.176952128630239</v>
       </c>
       <c r="E8" t="n">
-        <v>11.48392338928973</v>
+        <v>12.76671627375829</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.57380873473584</v>
+        <v>1.464078464906248</v>
       </c>
       <c r="C9" t="n">
-        <v>5.558014315913236</v>
+        <v>8.066883504287448</v>
       </c>
       <c r="D9" t="n">
-        <v>6.20601980198821</v>
+        <v>5.572624356449107</v>
       </c>
       <c r="E9" t="n">
-        <v>13.33784285263729</v>
+        <v>15.1035863256428</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.905919298137485</v>
+        <v>1.759214005032703</v>
       </c>
       <c r="C10" t="n">
-        <v>6.622165776751567</v>
+        <v>9.893587082068089</v>
       </c>
       <c r="D10" t="n">
-        <v>6.735470049546989</v>
+        <v>5.929026535279615</v>
       </c>
       <c r="E10" t="n">
-        <v>15.26355512443604</v>
+        <v>17.58182762238041</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.264197257423107</v>
+        <v>2.04897329896107</v>
       </c>
       <c r="C11" t="n">
-        <v>7.778087482713189</v>
+        <v>11.8001997552232</v>
       </c>
       <c r="D11" t="n">
-        <v>7.33850904923748</v>
+        <v>6.31462780400529</v>
       </c>
       <c r="E11" t="n">
-        <v>17.38079378937378</v>
+        <v>20.16380085818956</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.631770427590204</v>
+        <v>2.329100235194953</v>
       </c>
       <c r="C12" t="n">
-        <v>9.038635714253854</v>
+        <v>13.71942174336585</v>
       </c>
       <c r="D12" t="n">
-        <v>7.938622208315847</v>
+        <v>6.631598752099904</v>
       </c>
       <c r="E12" t="n">
-        <v>19.6090283501599</v>
+        <v>22.68012073066071</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.990674848681651</v>
+        <v>2.606150518669355</v>
       </c>
       <c r="C13" t="n">
-        <v>10.36174221803725</v>
+        <v>15.61503272765774</v>
       </c>
       <c r="D13" t="n">
-        <v>8.442284158765295</v>
+        <v>7.033087302311185</v>
       </c>
       <c r="E13" t="n">
-        <v>21.7947012254842</v>
+        <v>25.25427054863829</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.741875681736946</v>
+        <v>1.497626670397382</v>
       </c>
       <c r="C14" t="n">
-        <v>7.368369949545841</v>
+        <v>10.77332624227688</v>
       </c>
       <c r="D14" t="n">
-        <v>6.44664629993668</v>
+        <v>5.36565372026756</v>
       </c>
       <c r="E14" t="n">
-        <v>15.55689193121947</v>
+        <v>17.63660663294182</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.79141467089324</v>
+        <v>1.533224842153371</v>
       </c>
       <c r="C15" t="n">
-        <v>7.882059618315941</v>
+        <v>11.57221361913068</v>
       </c>
       <c r="D15" t="n">
-        <v>6.507406665352515</v>
+        <v>5.289813710114494</v>
       </c>
       <c r="E15" t="n">
-        <v>16.1808809545617</v>
+        <v>18.39525217139855</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.099064948973063</v>
+        <v>1.775284556112465</v>
       </c>
       <c r="C16" t="n">
-        <v>9.312574015651011</v>
+        <v>13.55370446304315</v>
       </c>
       <c r="D16" t="n">
-        <v>7.011828635794527</v>
+        <v>5.618924993009152</v>
       </c>
       <c r="E16" t="n">
-        <v>18.4234676004186</v>
+        <v>20.94791401216477</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.701162604441831</v>
+        <v>1.424849713081566</v>
       </c>
       <c r="C17" t="n">
-        <v>8.643139891079198</v>
+        <v>12.27634270757058</v>
       </c>
       <c r="D17" t="n">
-        <v>6.542877209906953</v>
+        <v>5.148235873685062</v>
       </c>
       <c r="E17" t="n">
-        <v>16.88717970542798</v>
+        <v>18.84942829433721</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.961993334506123</v>
+        <v>1.614268115138946</v>
       </c>
       <c r="C18" t="n">
-        <v>10.14755043811292</v>
+        <v>14.27546574025132</v>
       </c>
       <c r="D18" t="n">
-        <v>7.053680540426568</v>
+        <v>5.496952658233529</v>
       </c>
       <c r="E18" t="n">
-        <v>19.16322431304562</v>
+        <v>21.38668651362379</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.986615566928633</v>
+        <v>1.606522125752438</v>
       </c>
       <c r="C19" t="n">
-        <v>10.93606074173284</v>
+        <v>15.2150179281696</v>
       </c>
       <c r="D19" t="n">
-        <v>7.196848808136881</v>
+        <v>5.529006720777187</v>
       </c>
       <c r="E19" t="n">
-        <v>20.11952511679835</v>
+        <v>22.35054677469923</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.239170163846125</v>
+        <v>1.770562349655038</v>
       </c>
       <c r="C20" t="n">
-        <v>12.64422320730595</v>
+        <v>17.37705217489305</v>
       </c>
       <c r="D20" t="n">
-        <v>7.675431179003116</v>
+        <v>5.889730279748593</v>
       </c>
       <c r="E20" t="n">
-        <v>22.55882455015519</v>
+        <v>25.03734480429668</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.347478176509874</v>
+        <v>1.041113987922615</v>
       </c>
       <c r="C21" t="n">
-        <v>9.394412504277026</v>
+        <v>12.67998827617166</v>
       </c>
       <c r="D21" t="n">
-        <v>6.421199399442602</v>
+        <v>4.893973035762181</v>
       </c>
       <c r="E21" t="n">
-        <v>17.1630900802295</v>
+        <v>18.61507529985645</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_19_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.246717909904105</v>
+        <v>1.276327420664189</v>
       </c>
       <c r="C3" t="n">
-        <v>4.729684320750568</v>
+        <v>4.582245450526782</v>
       </c>
       <c r="D3" t="n">
-        <v>6.057643592279086</v>
+        <v>6.132708021745796</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03404582293376</v>
+        <v>11.99128089293677</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.373790676320513</v>
+        <v>1.433017028903647</v>
       </c>
       <c r="C4" t="n">
-        <v>5.407178795771109</v>
+        <v>4.978880652679051</v>
       </c>
       <c r="D4" t="n">
-        <v>6.263858932824904</v>
+        <v>6.436686661158508</v>
       </c>
       <c r="E4" t="n">
-        <v>13.04482840491653</v>
+        <v>12.8485843427412</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.545511253329686</v>
+        <v>1.641257646278413</v>
       </c>
       <c r="C5" t="n">
-        <v>6.334604218133103</v>
+        <v>5.468692220281333</v>
       </c>
       <c r="D5" t="n">
-        <v>6.512690500871828</v>
+        <v>6.771312086753733</v>
       </c>
       <c r="E5" t="n">
-        <v>14.39280597233462</v>
+        <v>13.88126195331348</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.738044040212375</v>
+        <v>1.892210030946742</v>
       </c>
       <c r="C6" t="n">
-        <v>7.468212795762913</v>
+        <v>6.076207164551609</v>
       </c>
       <c r="D6" t="n">
-        <v>6.729656458639666</v>
+        <v>7.144034505616763</v>
       </c>
       <c r="E6" t="n">
-        <v>15.93591329461495</v>
+        <v>15.11245170111511</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.950659489152204</v>
+        <v>2.174755001690417</v>
       </c>
       <c r="C7" t="n">
-        <v>8.746573548725184</v>
+        <v>6.836605084508474</v>
       </c>
       <c r="D7" t="n">
-        <v>7.030395265091879</v>
+        <v>7.507125870798375</v>
       </c>
       <c r="E7" t="n">
-        <v>17.72762830296926</v>
+        <v>16.51848595699727</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.181423621671696</v>
+        <v>1.382545025342426</v>
       </c>
       <c r="C8" t="n">
-        <v>6.408340523456359</v>
+        <v>4.612849570658296</v>
       </c>
       <c r="D8" t="n">
-        <v>5.176952128630239</v>
+        <v>5.794973561331592</v>
       </c>
       <c r="E8" t="n">
-        <v>12.76671627375829</v>
+        <v>11.79036815733231</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.464078464906248</v>
+        <v>1.755034559846244</v>
       </c>
       <c r="C9" t="n">
-        <v>8.066883504287448</v>
+        <v>5.717681746395377</v>
       </c>
       <c r="D9" t="n">
-        <v>5.572624356449107</v>
+        <v>6.420447707408306</v>
       </c>
       <c r="E9" t="n">
-        <v>15.1035863256428</v>
+        <v>13.89316401364993</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.759214005032703</v>
+        <v>2.145076775518022</v>
       </c>
       <c r="C10" t="n">
-        <v>9.893587082068089</v>
+        <v>6.989721004278892</v>
       </c>
       <c r="D10" t="n">
-        <v>5.929026535279615</v>
+        <v>7.022870609114214</v>
       </c>
       <c r="E10" t="n">
-        <v>17.58182762238041</v>
+        <v>16.15766838891113</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.04897329896107</v>
+        <v>2.543774805260369</v>
       </c>
       <c r="C11" t="n">
-        <v>11.8001997552232</v>
+        <v>8.366615741939816</v>
       </c>
       <c r="D11" t="n">
-        <v>6.31462780400529</v>
+        <v>7.534004244522255</v>
       </c>
       <c r="E11" t="n">
-        <v>20.16380085818956</v>
+        <v>18.44439479172244</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.329100235194953</v>
+        <v>2.963832489178807</v>
       </c>
       <c r="C12" t="n">
-        <v>13.71942174336585</v>
+        <v>9.797061386518303</v>
       </c>
       <c r="D12" t="n">
-        <v>6.631598752099904</v>
+        <v>8.077570971635883</v>
       </c>
       <c r="E12" t="n">
-        <v>22.68012073066071</v>
+        <v>20.83846484733299</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.606150518669355</v>
+        <v>3.394237897962137</v>
       </c>
       <c r="C13" t="n">
-        <v>15.61503272765774</v>
+        <v>11.23984497114701</v>
       </c>
       <c r="D13" t="n">
-        <v>7.033087302311185</v>
+        <v>8.580208103470476</v>
       </c>
       <c r="E13" t="n">
-        <v>25.25427054863829</v>
+        <v>23.21429097257963</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.497626670397382</v>
+        <v>1.96989640352531</v>
       </c>
       <c r="C14" t="n">
-        <v>10.77332624227688</v>
+        <v>7.782225694271084</v>
       </c>
       <c r="D14" t="n">
-        <v>5.36565372026756</v>
+        <v>6.506199115676291</v>
       </c>
       <c r="E14" t="n">
-        <v>17.63660663294182</v>
+        <v>16.25832121347268</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.533224842153371</v>
+        <v>2.067158148585042</v>
       </c>
       <c r="C15" t="n">
-        <v>11.57221361913068</v>
+        <v>8.374602441536567</v>
       </c>
       <c r="D15" t="n">
-        <v>5.289813710114494</v>
+        <v>6.552301987867723</v>
       </c>
       <c r="E15" t="n">
-        <v>18.39525217139855</v>
+        <v>16.99406257798933</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.775284556112465</v>
+        <v>2.45152219227471</v>
       </c>
       <c r="C16" t="n">
-        <v>13.55370446304315</v>
+        <v>9.8647972818128</v>
       </c>
       <c r="D16" t="n">
-        <v>5.618924993009152</v>
+        <v>7.10615495521856</v>
       </c>
       <c r="E16" t="n">
-        <v>20.94791401216477</v>
+        <v>19.42247442930607</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.424849713081566</v>
+        <v>2.001145432951486</v>
       </c>
       <c r="C17" t="n">
-        <v>12.27634270757058</v>
+        <v>9.116921515671665</v>
       </c>
       <c r="D17" t="n">
-        <v>5.148235873685062</v>
+        <v>6.638342356667914</v>
       </c>
       <c r="E17" t="n">
-        <v>18.84942829433721</v>
+        <v>17.75640930529106</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.614268115138946</v>
+        <v>2.326339542506199</v>
       </c>
       <c r="C18" t="n">
-        <v>14.27546574025132</v>
+        <v>10.59460889019579</v>
       </c>
       <c r="D18" t="n">
-        <v>5.496952658233529</v>
+        <v>7.103425696600755</v>
       </c>
       <c r="E18" t="n">
-        <v>21.38668651362379</v>
+        <v>20.02437412930275</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.606522125752438</v>
+        <v>2.378450710647621</v>
       </c>
       <c r="C19" t="n">
-        <v>15.2150179281696</v>
+        <v>11.28698645861586</v>
       </c>
       <c r="D19" t="n">
-        <v>5.529006720777187</v>
+        <v>7.237689512633549</v>
       </c>
       <c r="E19" t="n">
-        <v>22.35054677469923</v>
+        <v>20.90312668189703</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.770562349655038</v>
+        <v>2.693621176141974</v>
       </c>
       <c r="C20" t="n">
-        <v>17.37705217489305</v>
+        <v>12.93443764615834</v>
       </c>
       <c r="D20" t="n">
-        <v>5.889730279748593</v>
+        <v>7.679289447480805</v>
       </c>
       <c r="E20" t="n">
-        <v>25.03734480429668</v>
+        <v>23.30734826978112</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.041113987922615</v>
+        <v>1.626402516763436</v>
       </c>
       <c r="C21" t="n">
-        <v>12.67998827617166</v>
+        <v>9.446062250997452</v>
       </c>
       <c r="D21" t="n">
-        <v>4.893973035762181</v>
+        <v>6.410989223318437</v>
       </c>
       <c r="E21" t="n">
-        <v>18.61507529985645</v>
+        <v>17.48345399107933</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_19_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_19_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.276327420664189</v>
+        <v>2.597183621037339</v>
       </c>
       <c r="C3" t="n">
-        <v>4.582245450526782</v>
+        <v>7.78830969939392</v>
       </c>
       <c r="D3" t="n">
-        <v>6.132708021745796</v>
+        <v>8.165753057469564</v>
       </c>
       <c r="E3" t="n">
-        <v>11.99128089293677</v>
+        <v>18.55124637790082</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.433017028903647</v>
+        <v>1.075420387604204</v>
       </c>
       <c r="C4" t="n">
-        <v>4.978880652679051</v>
+        <v>4.674110919240472</v>
       </c>
       <c r="D4" t="n">
-        <v>6.436686661158508</v>
+        <v>5.869486263248234</v>
       </c>
       <c r="E4" t="n">
-        <v>12.8485843427412</v>
+        <v>11.61901757009291</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.641257646278413</v>
+        <v>1.163766641405438</v>
       </c>
       <c r="C5" t="n">
-        <v>5.468692220281333</v>
+        <v>5.494220105501272</v>
       </c>
       <c r="D5" t="n">
-        <v>6.771312086753733</v>
+        <v>6.191044585326801</v>
       </c>
       <c r="E5" t="n">
-        <v>13.88126195331348</v>
+        <v>12.84903133223351</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.892210030946742</v>
+        <v>1.253531217521732</v>
       </c>
       <c r="C6" t="n">
-        <v>6.076207164551609</v>
+        <v>6.509485778837202</v>
       </c>
       <c r="D6" t="n">
-        <v>7.144034505616763</v>
+        <v>6.661169040176363</v>
       </c>
       <c r="E6" t="n">
-        <v>15.11245170111511</v>
+        <v>14.4241860365353</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.174755001690417</v>
+        <v>1.337268150490706</v>
       </c>
       <c r="C7" t="n">
-        <v>6.836605084508474</v>
+        <v>7.648570985236907</v>
       </c>
       <c r="D7" t="n">
-        <v>7.507125870798375</v>
+        <v>7.091754298126266</v>
       </c>
       <c r="E7" t="n">
-        <v>16.51848595699727</v>
+        <v>16.07759343385388</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.382545025342426</v>
+        <v>1.417543566637594</v>
       </c>
       <c r="C8" t="n">
-        <v>4.612849570658296</v>
+        <v>8.927230220388001</v>
       </c>
       <c r="D8" t="n">
-        <v>5.794973561331592</v>
+        <v>7.571615782136442</v>
       </c>
       <c r="E8" t="n">
-        <v>11.79036815733231</v>
+        <v>17.91638956916204</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.755034559846244</v>
+        <v>1.484277979178811</v>
       </c>
       <c r="C9" t="n">
-        <v>5.717681746395377</v>
+        <v>10.35640834168693</v>
       </c>
       <c r="D9" t="n">
-        <v>6.420447707408306</v>
+        <v>8.086182579007582</v>
       </c>
       <c r="E9" t="n">
-        <v>13.89316401364993</v>
+        <v>19.92686889987333</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.145076775518022</v>
+        <v>0.9452365071258715</v>
       </c>
       <c r="C10" t="n">
-        <v>6.989721004278892</v>
+        <v>7.507935203181568</v>
       </c>
       <c r="D10" t="n">
-        <v>7.022870609114214</v>
+        <v>6.376470974037117</v>
       </c>
       <c r="E10" t="n">
-        <v>16.15766838891113</v>
+        <v>14.82964268434456</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.543774805260369</v>
+        <v>0.845078606338612</v>
       </c>
       <c r="C11" t="n">
-        <v>8.366615741939816</v>
+        <v>8.078526968889815</v>
       </c>
       <c r="D11" t="n">
-        <v>7.534004244522255</v>
+        <v>6.295918574903668</v>
       </c>
       <c r="E11" t="n">
-        <v>18.44439479172244</v>
+        <v>15.2195241501321</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.963832489178807</v>
+        <v>0.8781929564028569</v>
       </c>
       <c r="C12" t="n">
-        <v>9.797061386518303</v>
+        <v>9.598969455933892</v>
       </c>
       <c r="D12" t="n">
-        <v>8.077570971635883</v>
+        <v>6.797257857554343</v>
       </c>
       <c r="E12" t="n">
-        <v>20.83846484733299</v>
+        <v>17.27442026989109</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.394237897962137</v>
+        <v>0.676060921575481</v>
       </c>
       <c r="C13" t="n">
-        <v>11.23984497114701</v>
+        <v>9.135005308383892</v>
       </c>
       <c r="D13" t="n">
-        <v>8.580208103470476</v>
+        <v>6.273672171925435</v>
       </c>
       <c r="E13" t="n">
-        <v>23.21429097257963</v>
+        <v>16.08473840188481</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.96989640352531</v>
+        <v>0.7076830151292708</v>
       </c>
       <c r="C14" t="n">
-        <v>7.782225694271084</v>
+        <v>10.71358689447347</v>
       </c>
       <c r="D14" t="n">
-        <v>6.506199115676291</v>
+        <v>6.742996661940623</v>
       </c>
       <c r="E14" t="n">
-        <v>16.25832121347268</v>
+        <v>18.16426657154336</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.067158148585042</v>
+        <v>0.6666066911835843</v>
       </c>
       <c r="C15" t="n">
-        <v>8.374602441536567</v>
+        <v>11.56684345918845</v>
       </c>
       <c r="D15" t="n">
-        <v>6.552301987867723</v>
+        <v>6.843733793873388</v>
       </c>
       <c r="E15" t="n">
-        <v>16.99406257798933</v>
+        <v>19.07718394424543</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.45152219227471</v>
+        <v>0.7156842589188823</v>
       </c>
       <c r="C16" t="n">
-        <v>9.8647972818128</v>
+        <v>13.41343235106036</v>
       </c>
       <c r="D16" t="n">
-        <v>7.10615495521856</v>
+        <v>7.277106682959058</v>
       </c>
       <c r="E16" t="n">
-        <v>19.42247442930607</v>
+        <v>21.4062232929383</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.001145432951486</v>
+        <v>0.4312032266592841</v>
       </c>
       <c r="C17" t="n">
-        <v>9.116921515671665</v>
+        <v>9.959486847887407</v>
       </c>
       <c r="D17" t="n">
-        <v>6.638342356667914</v>
+        <v>6.086452884725568</v>
       </c>
       <c r="E17" t="n">
-        <v>17.75640930529106</v>
+        <v>16.47714295927226</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.326339542506199</v>
+        <v>0.328286614823091</v>
       </c>
       <c r="C18" t="n">
-        <v>10.59460889019579</v>
+        <v>8.829308708235519</v>
       </c>
       <c r="D18" t="n">
-        <v>7.103425696600755</v>
+        <v>5.606682599137194</v>
       </c>
       <c r="E18" t="n">
-        <v>20.02437412930275</v>
+        <v>14.7642779221958</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.378450710647621</v>
+        <v>0.377197285448667</v>
       </c>
       <c r="C19" t="n">
-        <v>11.28698645861586</v>
+        <v>10.81485417016652</v>
       </c>
       <c r="D19" t="n">
-        <v>7.237689512633549</v>
+        <v>6.203349583870236</v>
       </c>
       <c r="E19" t="n">
-        <v>20.90312668189703</v>
+        <v>17.39540103948542</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.693621176141974</v>
+        <v>0.4205708990222912</v>
       </c>
       <c r="C20" t="n">
-        <v>12.93443764615834</v>
+        <v>12.88263081980524</v>
       </c>
       <c r="D20" t="n">
-        <v>7.679289447480805</v>
+        <v>6.779910375620304</v>
       </c>
       <c r="E20" t="n">
-        <v>23.30734826978112</v>
+        <v>20.08311209444783</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.626402516763436</v>
+        <v>0.4615883181057229</v>
       </c>
       <c r="C21" t="n">
-        <v>9.446062250997452</v>
+        <v>15.06242488249852</v>
       </c>
       <c r="D21" t="n">
-        <v>6.410989223318437</v>
+        <v>7.322728498775407</v>
       </c>
       <c r="E21" t="n">
-        <v>17.48345399107933</v>
+        <v>22.84674169937965</v>
       </c>
     </row>
   </sheetData>
